--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
@@ -912,63 +912,66 @@
   </si>
   <si>
     <t>214
-145</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>R$ 731.824,02</t>
-  </si>
-  <si>
-    <t>R$ 4.752,10
-R$ 4.895,68</t>
-  </si>
-  <si>
-    <t>3.6%
-6.7%</t>
-  </si>
-  <si>
-    <t>51.7</t>
-  </si>
-  <si>
-    <t>(2.7%)</t>
-  </si>
-  <si>
-    <t>89.0%</t>
-  </si>
-  <si>
-    <t>37.3%</t>
-  </si>
-  <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>(0.1%)</t>
-  </si>
-  <si>
-    <t>26.7</t>
-  </si>
-  <si>
-    <t>73.3%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
+172</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 846.777,66</t>
+  </si>
+  <si>
+    <t>R$ 4.627,20
+R$ 4.731,05</t>
+  </si>
+  <si>
+    <t>3.2%
+5.5%</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>(3.7%)</t>
+  </si>
+  <si>
+    <t>84.2%</t>
+  </si>
+  <si>
+    <t>35.1%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>27.1</t>
+  </si>
+  <si>
+    <t>72.4%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
   </si>
   <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>7.1</t>
-  </si>
-  <si>
-    <t>18.7</t>
-  </si>
-  <si>
-    <t>73.0%</t>
-  </si>
-  <si>
-    <t>-R$ 15.947,92</t>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>71.7%</t>
+  </si>
+  <si>
+    <t>-R$ 16.837,31</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1750,7 +1753,9 @@
       <c r="AB3" s="8">
         <v>5.3421218181818189</v>
       </c>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="8">
+        <v>10.856363</v>
+      </c>
       <c r="AD3" s="8">
         <v>17.811818181818182</v>
       </c>
@@ -1879,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>5.0657226415094341</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>11.394024</v>
+      </c>
       <c r="AD4" s="8">
         <v>16.627358490566039</v>
       </c>
@@ -2008,7 +2015,9 @@
       <c r="AB5" s="8">
         <v>4.8784090909090914</v>
       </c>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="8">
+        <v>8.0165570000000006</v>
+      </c>
       <c r="AD5" s="8">
         <v>13.630000000000001</v>
       </c>
@@ -2230,7 +2239,9 @@
       <c r="AB7" s="8">
         <v>2.6597689655172414</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8">
+        <v>10.782686</v>
+      </c>
       <c r="AD7" s="8">
         <v>17.424732258064516</v>
       </c>
@@ -2361,7 +2372,9 @@
       <c r="AB8" s="8">
         <v>2.4206357142857144</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8">
+        <v>7.6420620000000001</v>
+      </c>
       <c r="AD8" s="8">
         <v>14.59047619047619</v>
       </c>
@@ -2490,7 +2503,9 @@
       <c r="AB9" s="8">
         <v>4.2564386363636366</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="8">
+        <v>8.7955690000000004</v>
+      </c>
       <c r="AD9" s="8">
         <v>14.655555555555555</v>
       </c>
@@ -2617,7 +2632,9 @@
       <c r="AB10" s="8">
         <v>2.5768292682926832</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>8.2455280000000002</v>
+      </c>
       <c r="AD10" s="8">
         <v>15.197560975609756</v>
       </c>
@@ -2746,7 +2763,9 @@
       <c r="AB11" s="8">
         <v>5.9784482758620694</v>
       </c>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="8">
+        <v>9.407826</v>
+      </c>
       <c r="AD11" s="8">
         <v>15.366953448275863</v>
       </c>
@@ -2875,7 +2894,9 @@
       <c r="AB12" s="8">
         <v>9.0127906976744185</v>
       </c>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="8">
+        <v>12.662411000000001</v>
+      </c>
       <c r="AD12" s="8">
         <v>19.014232584269664</v>
       </c>
@@ -3004,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>8.1264835616438358</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>14.424231000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>21.241441891891892</v>
       </c>
@@ -3107,10 +3130,10 @@
         <v>-0.070796460176991149</v>
       </c>
       <c r="T14" s="6">
-        <v>0.32581509262672104</v>
+        <v>0.37333436047800156</v>
       </c>
       <c r="U14" s="6">
-        <v>0.01053698728197373</v>
+        <v>0.058056255133254249</v>
       </c>
       <c r="V14" s="6">
         <v>0.039154359695791355</v>
@@ -3133,7 +3156,9 @@
       <c r="AB14" s="8">
         <v>2.7273584905660377</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>10.039858000000001</v>
+      </c>
       <c r="AD14" s="8">
         <v>16.726785714285715</v>
       </c>
@@ -3262,7 +3287,9 @@
       <c r="AB15" s="8">
         <v>3.0327160493827163</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>8.0943620000000003</v>
+      </c>
       <c r="AD15" s="8">
         <v>14.946385542168674</v>
       </c>
@@ -3389,7 +3416,9 @@
       <c r="AB16" s="8">
         <v>12.125</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="8">
+        <v>23.164393</v>
+      </c>
       <c r="AD16" s="8">
         <v>25.2270875</v>
       </c>
@@ -3518,7 +3547,9 @@
       <c r="AB17" s="8">
         <v>6.1991379310344827</v>
       </c>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="8">
+        <v>10.436438000000001</v>
+      </c>
       <c r="AD17" s="8">
         <v>18.192089830508476</v>
       </c>
@@ -3647,7 +3678,9 @@
       <c r="AB18" s="8">
         <v>6.2670000000000003</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8">
+        <v>10.694124</v>
+      </c>
       <c r="AD18" s="8">
         <v>17.39934705882353</v>
       </c>
@@ -3776,7 +3809,9 @@
       <c r="AB19" s="8">
         <v>7.0626679999999995</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>11.669076</v>
+      </c>
       <c r="AD19" s="8">
         <v>18.16281923076923</v>
       </c>
@@ -3905,7 +3940,9 @@
       <c r="AB20" s="8">
         <v>5.2716368421052628</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>9.8326530000000005</v>
+      </c>
       <c r="AD20" s="8">
         <v>16.604310344827585</v>
       </c>
@@ -4034,7 +4071,9 @@
       <c r="AB21" s="8">
         <v>2.440861290322581</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8">
+        <v>6.5795690000000002</v>
+      </c>
       <c r="AD21" s="8">
         <v>12.538170967741936</v>
       </c>
@@ -4163,7 +4202,9 @@
       <c r="AB22" s="8">
         <v>9.7323529411764707</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="8">
+        <v>15.228103000000001</v>
+      </c>
       <c r="AD22" s="8">
         <v>22.161111764705883</v>
       </c>
@@ -4292,7 +4333,9 @@
       <c r="AB23" s="8">
         <v>4.5234177215189879</v>
       </c>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="8">
+        <v>13.425856</v>
+      </c>
       <c r="AD23" s="8">
         <v>20.101625609756098</v>
       </c>
@@ -4516,7 +4559,9 @@
       <c r="AB25" s="8">
         <v>8.1228674418604658</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="8">
+        <v>13.185658</v>
+      </c>
       <c r="AD25" s="8">
         <v>20.060076744186048</v>
       </c>
@@ -4645,7 +4690,9 @@
       <c r="AB26" s="8">
         <v>10.453240277777777</v>
       </c>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="8">
+        <v>13.815277</v>
+      </c>
       <c r="AD26" s="8">
         <v>19.932000000000002</v>
       </c>
@@ -4774,7 +4821,9 @@
       <c r="AB27" s="8">
         <v>4.3260437500000002</v>
       </c>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="8">
+        <v>8.0666659999999997</v>
+      </c>
       <c r="AD27" s="8">
         <v>16.018750000000001</v>
       </c>
@@ -4998,7 +5047,9 @@
       <c r="AB29" s="8">
         <v>9.1057956521739136</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>14.687681</v>
+      </c>
       <c r="AD29" s="8">
         <v>22.61304347826087</v>
       </c>
@@ -5049,7 +5100,7 @@
         <v>19550</v>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C30" s="4">
         <v>44</v>
@@ -5085,25 +5136,57 @@
       <c t="s" r="N30" s="4">
         <v>52</v>
       </c>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
+      <c r="O30" s="5">
+        <v>4401.7200000000003</v>
+      </c>
+      <c r="P30" s="5">
+        <v>4401.7200000000003</v>
+      </c>
       <c r="Q30" s="6"/>
-      <c r="R30" s="7"/>
+      <c r="R30" s="7">
+        <v>34</v>
+      </c>
       <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
-      <c r="X30" s="8"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="8"/>
-      <c r="AB30" s="8"/>
-      <c r="AC30" s="8"/>
-      <c r="AD30" s="8"/>
-      <c r="AE30" s="6"/>
+      <c r="T30" s="6">
+        <v>0.35525610443190386</v>
+      </c>
+      <c r="U30" s="6">
+        <v>0.013392014939614514</v>
+      </c>
+      <c r="V30" s="6">
+        <v>0.044009273647574128</v>
+      </c>
+      <c r="W30" s="6">
+        <v>0.0082437092772825148</v>
+      </c>
+      <c r="X30" s="8">
+        <v>34.300000000000004</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA30" s="8">
+        <v>3.1185714285714288</v>
+      </c>
+      <c r="AB30" s="8">
+        <v>12.755558333333333</v>
+      </c>
+      <c r="AC30" s="8">
+        <v>16.168375000000001</v>
+      </c>
+      <c r="AD30" s="8">
+        <v>23.073608333333336</v>
+      </c>
+      <c r="AE30" s="6">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="AF30" s="9"/>
-      <c r="AG30" s="5"/>
+      <c r="AG30" s="5">
+        <v>-351.51999999999998</v>
+      </c>
       <c r="AH30" s="10">
         <v>3</v>
       </c>
@@ -5224,7 +5307,9 @@
       <c r="AB31" s="8">
         <v>4.4995228571428578</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="8">
+        <v>9.4612339999999993</v>
+      </c>
       <c r="AD31" s="8">
         <v>16.944594594594594</v>
       </c>
@@ -5353,7 +5438,9 @@
       <c r="AB32" s="8">
         <v>4.7419191919191919</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>7.1638659999999996</v>
+      </c>
       <c r="AD32" s="8">
         <v>13.046295959595959</v>
       </c>
@@ -5480,7 +5567,9 @@
       <c r="AB33" s="8">
         <v>6.2117108108108114</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8">
+        <v>8.8342329999999993</v>
+      </c>
       <c r="AD33" s="8">
         <v>15.798648648648648</v>
       </c>
@@ -5680,10 +5769,10 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="T35" s="6">
-        <v>0.31666043946700351</v>
+        <v>2.1446731934845191</v>
       </c>
       <c r="U35" s="6">
-        <v>-1.8369829582032624</v>
+        <v>-0.0089702041857470816</v>
       </c>
       <c r="V35" s="6">
         <v>0.056572448892829814</v>
@@ -5706,7 +5795,9 @@
       <c r="AB35" s="8">
         <v>2.3243576923076925</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="8">
+        <v>4.6980750000000002</v>
+      </c>
       <c r="AD35" s="8">
         <v>11.652565384615384</v>
       </c>
@@ -5759,7 +5850,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5795,25 +5886,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>2459.5599999999999</v>
+      </c>
+      <c r="P36" s="5">
+        <v>2459.5599999999999</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.02268103503083474</v>
+      </c>
+      <c r="R36" s="7">
+        <v>34</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.21428571428571419</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.30403246922213734</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.015406780074484868</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.08579928930377792</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.0073381011237782373</v>
+      </c>
+      <c r="X36" s="8">
+        <v>29.94111333333333</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>4.4854156249999999</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>9.0733333333333324</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>21.751113333333333</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>-164.69999999999999</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -5932,7 +6057,9 @@
       <c r="AB37" s="8">
         <v>10.330629729729729</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="8">
+        <v>16.884796000000001</v>
+      </c>
       <c r="AD37" s="8">
         <v>22.7316675</v>
       </c>
@@ -6061,7 +6188,9 @@
       <c r="AB38" s="8">
         <v>5.0816650000000001</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="8">
+        <v>8.4839380000000002</v>
+      </c>
       <c r="AD38" s="8">
         <v>14.841668181818182</v>
       </c>
@@ -6112,7 +6241,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6148,25 +6277,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>6664.1499999999996</v>
+      </c>
+      <c r="P39" s="5">
+        <v>6664.1499999999996</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.23518149197075955</v>
+      </c>
+      <c r="R39" s="7">
+        <v>77</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0.24193548387096775</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.27073647802045275</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.042955440678856274</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.077321864003661381</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.040274378577913161</v>
+      </c>
+      <c r="X39" s="8">
+        <v>20.315941304347827</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.2549554054054055</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>5.756480555555556</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>7.865901</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>13.696015217391304</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.89130434782608692</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6285,7 +6450,9 @@
       <c r="AB40" s="8">
         <v>4.5771821428571426</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>7.1973370000000001</v>
+      </c>
       <c r="AD40" s="8">
         <v>13.980232558139534</v>
       </c>
@@ -6414,7 +6581,9 @@
       <c r="AB41" s="8">
         <v>10.951852777777779</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8">
+        <v>13.555697</v>
+      </c>
       <c r="AD41" s="8">
         <v>18.445725641025639</v>
       </c>
@@ -6465,7 +6634,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6501,25 +6670,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>5580.8599999999997</v>
+      </c>
+      <c r="P42" s="5">
+        <v>5580.8599999999997</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.060440716716022469</v>
+      </c>
+      <c r="R42" s="7">
+        <v>51</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.2153846153846154</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.31090333747845317</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.035590930430077085</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.046333450400117542</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0075204359184785144</v>
+      </c>
+      <c r="X42" s="8">
+        <v>24.214813888888887</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.015625</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>5.4025242424242421</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>12.063173000000001</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>18.368519444444445</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.86111111111111116</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -6638,7 +6843,9 @@
       <c r="AB43" s="8">
         <v>5.8661764705882353</v>
       </c>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="8">
+        <v>11.357364</v>
+      </c>
       <c r="AD43" s="8">
         <v>17.741428571428571</v>
       </c>
@@ -6767,7 +6974,9 @@
       <c r="AB44" s="8">
         <v>8.5600868421052638</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>11.37467</v>
+      </c>
       <c r="AD44" s="8">
         <v>18.71875</v>
       </c>
@@ -6896,7 +7105,9 @@
       <c r="AB45" s="8">
         <v>3.654925</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>8.3290369999999996</v>
+      </c>
       <c r="AD45" s="8">
         <v>14.456666666666665</v>
       </c>
@@ -6947,7 +7158,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>44</v>
@@ -6981,25 +7192,59 @@
       <c t="s" r="N46" s="4">
         <v>52</v>
       </c>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
+      <c r="O46" s="5">
+        <v>6684.4099999999999</v>
+      </c>
+      <c r="P46" s="5">
+        <v>6684.4099999999999</v>
+      </c>
       <c r="Q46" s="6"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="8"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="8"/>
-      <c r="AB46" s="8"/>
-      <c r="AC46" s="8"/>
-      <c r="AD46" s="8"/>
-      <c r="AE46" s="6"/>
+      <c r="R46" s="7">
+        <v>64</v>
+      </c>
+      <c r="S46" s="6">
+        <v>0.33333333333333326</v>
+      </c>
+      <c r="T46" s="6">
+        <v>0.36325925549150934</v>
+      </c>
+      <c r="U46" s="6">
+        <v>-0.034092193626662638</v>
+      </c>
+      <c r="V46" s="6">
+        <v>0.03267124548015457</v>
+      </c>
+      <c r="W46" s="6">
+        <v>-0.018108105277803127</v>
+      </c>
+      <c r="X46" s="8">
+        <v>25.956861764705884</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="6">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AA46" s="8">
+        <v>4.7666666666666666</v>
+      </c>
+      <c r="AB46" s="8">
+        <v>7.624242424242424</v>
+      </c>
+      <c r="AC46" s="8">
+        <v>12.483555000000001</v>
+      </c>
+      <c r="AD46" s="8">
+        <v>19.169608823529412</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>0.82352941176470584</v>
+      </c>
       <c r="AF46" s="9"/>
-      <c r="AG46" s="5"/>
+      <c r="AG46" s="5">
+        <v>41.759999999999998</v>
+      </c>
       <c r="AH46" s="10">
         <v>3</v>
       </c>
@@ -7118,7 +7363,9 @@
       <c r="AB47" s="8">
         <v>7.5680265306122454</v>
       </c>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="8">
+        <v>14.482652</v>
+      </c>
       <c r="AD47" s="8">
         <v>21.434014285714284</v>
       </c>
@@ -7245,7 +7492,9 @@
       <c r="AB48" s="8">
         <v>4.8959459459459458</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>12.301646</v>
+      </c>
       <c r="AD48" s="8">
         <v>19.086402631578949</v>
       </c>
@@ -7372,7 +7621,9 @@
       <c r="AB49" s="8">
         <v>12.498958333333334</v>
       </c>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="8">
+        <v>16.530555</v>
+      </c>
       <c r="AD49" s="8">
         <v>24.449306250000003</v>
       </c>
@@ -7423,7 +7674,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7459,25 +7710,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>5771.6400000000003</v>
+      </c>
+      <c r="P50" s="5">
+        <v>5771.6400000000003</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>0.25234666909687431</v>
+      </c>
+      <c r="R50" s="7">
+        <v>65</v>
+      </c>
+      <c r="S50" s="6">
+        <v>0.18181818181818188</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.26104907790506682</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.073528269261423085</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.069307163994982365</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.02875716434150432</v>
+      </c>
+      <c r="X50" s="8">
+        <v>21.935058620689656</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.8522442307692306</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>3.9791678571428575</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>6.9581520000000001</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>14.549999999999999</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.96551724137931039</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7518,7 +7805,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7554,25 +7841,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>917.69000000000005</v>
+      </c>
+      <c r="P51" s="5">
+        <v>917.69000000000005</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.16738645230361648</v>
+      </c>
+      <c r="R51" s="7">
+        <v>9</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.32212402881147228</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.040283211106146952</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.099208338327757745</v>
+      </c>
+      <c r="X51" s="8">
+        <v>16.783340000000003</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>2.1388888888888888</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>5.5499999999999998</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>14.073339999999998</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -7691,7 +8012,9 @@
       <c r="AB52" s="8">
         <v>6.3172413793103441</v>
       </c>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="8">
+        <v>10.932240999999999</v>
+      </c>
       <c r="AD52" s="8">
         <v>18.609999999999999</v>
       </c>
@@ -7818,7 +8141,9 @@
       <c r="AB53" s="8">
         <v>2.2602576923076922</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>4.7238360000000004</v>
+      </c>
       <c r="AD53" s="8">
         <v>11.680769230769231</v>
       </c>
@@ -7869,7 +8194,7 @@
         <v>19609</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C54" s="4">
         <v>44</v>
@@ -7905,25 +8230,61 @@
       <c t="s" r="N54" s="4">
         <v>52</v>
       </c>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="8"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="6"/>
-      <c r="AA54" s="8"/>
-      <c r="AB54" s="8"/>
-      <c r="AC54" s="8"/>
-      <c r="AD54" s="8"/>
-      <c r="AE54" s="6"/>
+      <c r="O54" s="5">
+        <v>2605.79</v>
+      </c>
+      <c r="P54" s="5">
+        <v>2605.79</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>-0.12138122180337052</v>
+      </c>
+      <c r="R54" s="7">
+        <v>31</v>
+      </c>
+      <c r="S54" s="6">
+        <v>-0.16216216216216217</v>
+      </c>
+      <c r="T54" s="6">
+        <v>1.3614998906281781</v>
+      </c>
+      <c r="U54" s="6">
+        <v>1.0165488393155244</v>
+      </c>
+      <c r="V54" s="6">
+        <v>0.03278103761239394</v>
+      </c>
+      <c r="W54" s="6">
+        <v>-0.035939005061804676</v>
+      </c>
+      <c r="X54" s="8">
+        <v>47.216000000000001</v>
+      </c>
+      <c r="Y54" s="6">
+        <v>0.44</v>
+      </c>
+      <c r="Z54" s="6">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="AA54" s="8">
+        <v>5.6021516129032252</v>
+      </c>
+      <c r="AB54" s="8">
+        <v>15.719445833333333</v>
+      </c>
+      <c r="AC54" s="8">
+        <v>21.415444000000001</v>
+      </c>
+      <c r="AD54" s="8">
+        <v>27.495999999999999</v>
+      </c>
+      <c r="AE54" s="6">
+        <v>0.32000000000000001</v>
+      </c>
       <c r="AF54" s="9"/>
-      <c r="AG54" s="5"/>
+      <c r="AG54" s="5">
+        <v>0</v>
+      </c>
       <c r="AH54" s="10">
         <v>2</v>
       </c>
@@ -7964,7 +8325,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8000,25 +8361,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>2752</v>
+      </c>
+      <c r="P55" s="5">
+        <v>2752</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>-0.34079095503868539</v>
+      </c>
+      <c r="R55" s="7">
+        <v>40</v>
+      </c>
+      <c r="S55" s="6">
+        <v>-0.11111111111111116</v>
+      </c>
+      <c r="T55" s="6">
+        <v>-0.0003015988372093023</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.33944040697674416</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.039454033430232557</v>
+      </c>
+      <c r="W55" s="6">
+        <v>-0.031665152616279071</v>
+      </c>
+      <c r="X55" s="8">
+        <v>38.82205882352941</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.44117647058823528</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>2.1418707317073169</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>20.72009705882353</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>22.715812</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>29.57255</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.14705882352941177</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8135,7 +8532,9 @@
       <c r="AB56" s="8">
         <v>4.8885714285714288</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>10.021219</v>
+      </c>
       <c r="AD56" s="8">
         <v>18.221917808219178</v>
       </c>
@@ -8264,7 +8663,9 @@
       <c r="AB57" s="8">
         <v>15.022413793103448</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>23.874433</v>
+      </c>
       <c r="AD57" s="8">
         <v>28.685937500000001</v>
       </c>
@@ -8365,7 +8766,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>17.158974000000001</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -8488,7 +8891,9 @@
       <c r="AB59" s="8">
         <v>2.9431818181818183</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="8">
+        <v>5.9378770000000003</v>
+      </c>
       <c r="AD59" s="8">
         <v>12.882577272727273</v>
       </c>
@@ -8617,7 +9022,9 @@
       <c r="AB60" s="8">
         <v>3.4407444444444444</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8">
+        <v>9.5657399999999999</v>
+      </c>
       <c r="AD60" s="8">
         <v>15.069050000000001</v>
       </c>
@@ -8744,7 +9151,9 @@
       <c r="AB61" s="8">
         <v>5.0166699999999995</v>
       </c>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="8">
+        <v>6.0138879999999997</v>
+      </c>
       <c r="AD61" s="8">
         <v>11.7125</v>
       </c>
@@ -8793,7 +9202,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>44</v>
@@ -8829,25 +9238,61 @@
       <c t="s" r="N62" s="4">
         <v>52</v>
       </c>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="8"/>
-      <c r="Y62" s="6"/>
-      <c r="Z62" s="6"/>
-      <c r="AA62" s="8"/>
-      <c r="AB62" s="8"/>
-      <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="6"/>
+      <c r="O62" s="5">
+        <v>3369.1799999999998</v>
+      </c>
+      <c r="P62" s="5">
+        <v>3369.1799999999998</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>-0.416727547201169</v>
+      </c>
+      <c r="R62" s="7">
+        <v>32</v>
+      </c>
+      <c r="S62" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="T62" s="6">
+        <v>0.0015758433802883789</v>
+      </c>
+      <c r="U62" s="6">
+        <v>-0.29866041588754533</v>
+      </c>
+      <c r="V62" s="6">
+        <v>0.02089558883764002</v>
+      </c>
+      <c r="W62" s="6">
+        <v>-0.0037157409221234843</v>
+      </c>
+      <c r="X62" s="8">
+        <v>18.889130434782608</v>
+      </c>
+      <c r="Y62" s="6">
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="Z62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="8">
+        <v>2.7215676470588233</v>
+      </c>
+      <c r="AB62" s="8">
+        <v>3.1181818181818177</v>
+      </c>
+      <c r="AC62" s="8">
+        <v>6.0073109999999996</v>
+      </c>
+      <c r="AD62" s="8">
+        <v>12.631160869565218</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>1</v>
+      </c>
       <c r="AF62" s="9"/>
-      <c r="AG62" s="5"/>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
       <c r="AH62" s="10">
         <v>4</v>
       </c>
@@ -8966,7 +9411,9 @@
       <c r="AB63" s="8">
         <v>18.332000000000001</v>
       </c>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="8">
+        <v>21.711333</v>
+      </c>
       <c r="AD63" s="8">
         <v>27.599332</v>
       </c>
@@ -9093,7 +9540,9 @@
       <c r="AB64" s="8">
         <v>4.0771947368421051</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8">
+        <v>9.8026300000000006</v>
+      </c>
       <c r="AD64" s="8">
         <v>16.737721052631581</v>
       </c>
@@ -9289,10 +9738,10 @@
         <v>-0.022222222222222254</v>
       </c>
       <c r="T66" s="6">
-        <v>0.34833499271012569</v>
+        <v>0.37253317221178722</v>
       </c>
       <c r="U66" s="6">
-        <v>-0.014340850879382134</v>
+        <v>0.0098573286222794331</v>
       </c>
       <c r="V66" s="6">
         <v>0.032626719031169135</v>
@@ -9315,7 +9764,9 @@
       <c r="AB66" s="8">
         <v>6.4962962962962969</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>10.445677999999999</v>
+      </c>
       <c r="AD66" s="8">
         <v>16.760714285714286</v>
       </c>
@@ -9442,7 +9893,9 @@
       <c r="AB67" s="8">
         <v>16.796341463414635</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="8">
+        <v>22.669917999999999</v>
+      </c>
       <c r="AD67" s="8">
         <v>29.567480487804875</v>
       </c>
@@ -9571,7 +10024,9 @@
       <c r="AB68" s="8">
         <v>2.6521516129032259</v>
       </c>
-      <c r="AC68" s="8"/>
+      <c r="AC68" s="8">
+        <v>7.1865579999999998</v>
+      </c>
       <c r="AD68" s="8">
         <v>14.14516129032258</v>
       </c>
@@ -9715,7 +10170,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>44</v>
@@ -9751,25 +10206,61 @@
       <c t="s" r="N70" s="4">
         <v>52</v>
       </c>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="7"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
-      <c r="V70" s="6"/>
-      <c r="W70" s="6"/>
-      <c r="X70" s="8"/>
-      <c r="Y70" s="6"/>
-      <c r="Z70" s="6"/>
-      <c r="AA70" s="8"/>
-      <c r="AB70" s="8"/>
-      <c r="AC70" s="8"/>
-      <c r="AD70" s="8"/>
-      <c r="AE70" s="6"/>
+      <c r="O70" s="5">
+        <v>4451.1199999999999</v>
+      </c>
+      <c r="P70" s="5">
+        <v>4451.1199999999999</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>0.28720979999768637</v>
+      </c>
+      <c r="R70" s="7">
+        <v>50</v>
+      </c>
+      <c r="S70" s="6">
+        <v>0.31578947368421062</v>
+      </c>
+      <c r="T70" s="6">
+        <v>2.7890032171678141</v>
+      </c>
+      <c r="U70" s="6">
+        <v>2.431958248710437</v>
+      </c>
+      <c r="V70" s="6">
+        <v>0.013152532396340696</v>
+      </c>
+      <c r="W70" s="6">
+        <v>-0.0043486807814662378</v>
+      </c>
+      <c r="X70" s="8">
+        <v>32.933823529411768</v>
+      </c>
+      <c r="Y70" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z70" s="6">
+        <v>0.20588235294117646</v>
+      </c>
+      <c r="AA70" s="8">
+        <v>8.0766659999999995</v>
+      </c>
+      <c r="AB70" s="8">
+        <v>9.412255882352941</v>
+      </c>
+      <c r="AC70" s="8">
+        <v>18.262253999999999</v>
+      </c>
+      <c r="AD70" s="8">
+        <v>25.207844117647056</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>0.38235294117647056</v>
+      </c>
       <c r="AF70" s="9"/>
-      <c r="AG70" s="5"/>
+      <c r="AG70" s="5">
+        <v>-22.800000000000001</v>
+      </c>
       <c r="AH70" s="10">
         <v>2</v>
       </c>
@@ -9810,7 +10301,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9844,25 +10335,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>5941.1300000000001</v>
+      </c>
+      <c r="P71" s="5">
+        <v>5941.1300000000001</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0.14365325792560735</v>
+      </c>
+      <c r="R71" s="7">
+        <v>70</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.090909090909090939</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.28164763268940418</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.042800746659305548</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.066880122131648359</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.023070274510067951</v>
+      </c>
+      <c r="X71" s="8">
+        <v>20.773214285714285</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>3.7176772727272729</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>4.7406680000000003</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>8.59511</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>15.013689285714287</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>0</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -9979,7 +10506,9 @@
       <c r="AB72" s="8">
         <v>8.4686142857142865</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>12.710172</v>
+      </c>
       <c r="AD72" s="8">
         <v>19.623159740259741</v>
       </c>
@@ -10106,7 +10635,9 @@
       <c r="AB73" s="8">
         <v>6.0777777777777784</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="8">
+        <v>10.120369</v>
+      </c>
       <c r="AD73" s="8">
         <v>18.063888888888886</v>
       </c>
@@ -10248,7 +10779,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10284,25 +10815,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>4298.54</v>
+      </c>
+      <c r="P75" s="5">
+        <v>4298.54</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>0.31217871228494332</v>
+      </c>
+      <c r="R75" s="7">
+        <v>50</v>
+      </c>
+      <c r="S75" s="6">
+        <v>0.38888888888888884</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.30584803212253464</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.048527872254300296</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.02108134389816077</v>
+      </c>
+      <c r="X75" s="8">
+        <v>31.629999999999999</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>5.4850346938775516</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>11.82389</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>17.182776</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>24.113890000000001</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.46666666666666667</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>0</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10343,7 +10910,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10377,25 +10944,59 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
+      <c r="O76" s="5">
+        <v>6783.8199999999997</v>
+      </c>
+      <c r="P76" s="5">
+        <v>6783.8199999999997</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0.22728539122568958</v>
+      </c>
+      <c r="R76" s="7">
+        <v>80</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.047619047619047672</v>
+      </c>
+      <c r="T76" s="6">
+        <v>-0.10289161563838664</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.48110182758386871</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.057975742280897788</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.027924827014867731</v>
+      </c>
+      <c r="X76" s="8">
+        <v>25.560638297872337</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.5957446808510638</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.063829787234042548</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>3.08770875</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>4.1769833333333333</v>
+      </c>
       <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="AD76" s="8">
+        <v>15.428014893617021</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.72340425531914898</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-151.69999999999999</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -10514,7 +11115,9 @@
       <c r="AB77" s="8">
         <v>4.9063476190476187</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8">
+        <v>9.5341260000000005</v>
+      </c>
       <c r="AD77" s="8">
         <v>16.472223809523808</v>
       </c>
@@ -10639,7 +11242,9 @@
       <c r="AB78" s="8">
         <v>7.0477272727272728</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="8">
+        <v>9.8681809999999999</v>
+      </c>
       <c r="AD78" s="8">
         <v>17.835984090909093</v>
       </c>
@@ -10768,7 +11373,9 @@
       <c r="AB79" s="8">
         <v>15.881861764705882</v>
       </c>
-      <c r="AC79" s="8"/>
+      <c r="AC79" s="8">
+        <v>20.594116</v>
+      </c>
       <c r="AD79" s="8">
         <v>27.531861764705884</v>
       </c>
@@ -10895,7 +11502,9 @@
       <c r="AB80" s="8">
         <v>2.8947937499999998</v>
       </c>
-      <c r="AC80" s="8"/>
+      <c r="AC80" s="8">
+        <v>7.1439570000000003</v>
+      </c>
       <c r="AD80" s="8">
         <v>16.037721052631579</v>
       </c>
@@ -11022,7 +11631,9 @@
       <c r="AB81" s="8">
         <v>6.2190476190476192</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>9.5888880000000007</v>
+      </c>
       <c r="AD81" s="8">
         <v>16.545238095238094</v>
       </c>
@@ -11151,7 +11762,9 @@
       <c r="AB82" s="8">
         <v>7.0171558823529416</v>
       </c>
-      <c r="AC82" s="8"/>
+      <c r="AC82" s="8">
+        <v>11.477449999999999</v>
+      </c>
       <c r="AD82" s="8">
         <v>18.38578529411765</v>
       </c>
@@ -11373,7 +11986,9 @@
       <c r="AB84" s="8">
         <v>9.9783349999999995</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="8">
+        <v>17.261666000000002</v>
+      </c>
       <c r="AD84" s="8">
         <v>23.633333333333333</v>
       </c>
@@ -11502,7 +12117,9 @@
       <c r="AB85" s="8">
         <v>4.7033399999999999</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="8">
+        <v>10.269999</v>
+      </c>
       <c r="AD85" s="8">
         <v>14.302087500000001</v>
       </c>
@@ -11631,7 +12248,9 @@
       <c r="AB86" s="8">
         <v>6.7095250000000002</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="8">
+        <v>17.139284</v>
+      </c>
       <c r="AD86" s="8">
         <v>25.595239285714285</v>
       </c>
@@ -11760,7 +12379,9 @@
       <c r="AB87" s="8">
         <v>2.4702357142857143</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="8">
+        <v>6.0781739999999997</v>
+      </c>
       <c r="AD87" s="8">
         <v>11.092061904761906</v>
       </c>
@@ -11887,7 +12508,9 @@
       <c r="AB88" s="8">
         <v>8.4718379310344822</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="8">
+        <v>11.384615999999999</v>
+      </c>
       <c r="AD88" s="8">
         <v>17.6523</v>
       </c>
@@ -12109,7 +12732,9 @@
       <c r="AB90" s="8">
         <v>26.158333333333335</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>42.136826999999997</v>
+      </c>
       <c r="AD90" s="8">
         <v>48.07741935483871</v>
       </c>
@@ -12238,7 +12863,9 @@
       <c r="AB91" s="8">
         <v>4.5147628571428564</v>
       </c>
-      <c r="AC91" s="8"/>
+      <c r="AC91" s="8">
+        <v>10.767913999999999</v>
+      </c>
       <c r="AD91" s="8">
         <v>17.547222222222224</v>
       </c>
@@ -12367,7 +12994,9 @@
       <c r="AB92" s="8">
         <v>14.674604761904762</v>
       </c>
-      <c r="AC92" s="8"/>
+      <c r="AC92" s="8">
+        <v>21.875395999999999</v>
+      </c>
       <c r="AD92" s="8">
         <v>29.775395238095239</v>
       </c>
@@ -12494,7 +13123,9 @@
       <c r="AB93" s="8">
         <v>2.4447368421052631</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="8">
+        <v>4.8553179999999996</v>
+      </c>
       <c r="AD93" s="8">
         <v>11.259523809523809</v>
       </c>
@@ -12621,7 +13252,9 @@
       <c r="AB94" s="8">
         <v>2.3153846153846156</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="8">
+        <v>5.7987169999999999</v>
+      </c>
       <c r="AD94" s="8">
         <v>12.907780000000001</v>
       </c>
@@ -12843,7 +13476,9 @@
       <c r="AB96" s="8">
         <v>3.6712121212121214</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="8">
+        <v>6.3114080000000001</v>
+      </c>
       <c r="AD96" s="8">
         <v>13.294948484848485</v>
       </c>
@@ -12972,7 +13607,9 @@
       <c r="AB97" s="8">
         <v>2.9483350000000002</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="8">
+        <v>7.3289989999999996</v>
+      </c>
       <c r="AD97" s="8">
         <v>12.350695833333333</v>
       </c>
@@ -13101,7 +13738,9 @@
       <c r="AB98" s="8">
         <v>14.74762142857143</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>27.718914999999999</v>
+      </c>
       <c r="AD98" s="8">
         <v>30.923150000000003</v>
       </c>
@@ -13230,7 +13869,9 @@
       <c r="AB99" s="8">
         <v>5.284058695652174</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>8.1478859999999997</v>
+      </c>
       <c r="AD99" s="8">
         <v>14.907802127659574</v>
       </c>
@@ -13359,7 +14000,9 @@
       <c r="AB100" s="8">
         <v>7.1891038461538459</v>
       </c>
-      <c r="AC100" s="8"/>
+      <c r="AC100" s="8">
+        <v>11.345511999999999</v>
+      </c>
       <c r="AD100" s="8">
         <v>20.300642307692307</v>
       </c>
@@ -13486,7 +14129,9 @@
       <c r="AB101" s="8">
         <v>17.990803448275862</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="8">
+        <v>21.754866</v>
+      </c>
       <c r="AD101" s="8">
         <v>27.360216129032256</v>
       </c>
@@ -13537,7 +14182,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -13573,25 +14218,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>2728.5999999999999</v>
+      </c>
+      <c r="P102" s="5">
+        <v>2728.5999999999999</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.31942722740049934</v>
+      </c>
+      <c r="R102" s="7">
+        <v>28</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.4285714285714286</v>
+      </c>
+      <c r="T102" s="6">
+        <v>4.1193285934178702E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.31735234186029465</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.020722714945393243</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0099816755845488526</v>
+      </c>
+      <c r="X102" s="8">
+        <v>62.934128571428573</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>7.0097689655172415</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>37.454165000000003</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>49.75</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -13632,7 +14311,7 @@
         <v>19720</v>
       </c>
       <c r="B103" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C103" s="4">
         <v>44</v>
@@ -13668,25 +14347,61 @@
       <c t="s" r="N103" s="4">
         <v>52</v>
       </c>
-      <c r="O103" s="5"/>
-      <c r="P103" s="5"/>
-      <c r="Q103" s="6"/>
-      <c r="R103" s="7"/>
-      <c r="S103" s="6"/>
-      <c r="T103" s="6"/>
-      <c r="U103" s="6"/>
-      <c r="V103" s="6"/>
-      <c r="W103" s="6"/>
-      <c r="X103" s="8"/>
-      <c r="Y103" s="6"/>
-      <c r="Z103" s="6"/>
-      <c r="AA103" s="8"/>
-      <c r="AB103" s="8"/>
-      <c r="AC103" s="8"/>
-      <c r="AD103" s="8"/>
-      <c r="AE103" s="6"/>
+      <c r="O103" s="5">
+        <v>4527.6499999999996</v>
+      </c>
+      <c r="P103" s="5">
+        <v>4527.6499999999996</v>
+      </c>
+      <c r="Q103" s="6">
+        <v>0.092416192558063104</v>
+      </c>
+      <c r="R103" s="7">
+        <v>48</v>
+      </c>
+      <c r="S103" s="6">
+        <v>-0.058823529411764719</v>
+      </c>
+      <c r="T103" s="6">
+        <v>0.52470137930272887</v>
+      </c>
+      <c r="U103" s="6">
+        <v>0.19288907048910583</v>
+      </c>
+      <c r="V103" s="6">
+        <v>0.2492840656852893</v>
+      </c>
+      <c r="W103" s="6">
+        <v>0.17955694455180946</v>
+      </c>
+      <c r="X103" s="8">
+        <v>29.832258064516129</v>
+      </c>
+      <c r="Y103" s="6">
+        <v>0.78125</v>
+      </c>
+      <c r="Z103" s="6">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="AA103" s="8">
+        <v>6.6187499999999995</v>
+      </c>
+      <c r="AB103" s="8">
+        <v>1.6781620689655172</v>
+      </c>
+      <c r="AC103" s="8">
+        <v>8.4278779999999998</v>
+      </c>
+      <c r="AD103" s="8">
+        <v>14.288170967741936</v>
+      </c>
+      <c r="AE103" s="6">
+        <v>0.77419354838709675</v>
+      </c>
       <c r="AF103" s="9"/>
-      <c r="AG103" s="5"/>
+      <c r="AG103" s="5">
+        <v>0</v>
+      </c>
       <c r="AH103" s="10">
         <v>2</v>
       </c>
@@ -13805,7 +14520,9 @@
       <c r="AB104" s="8">
         <v>2.3277777777777775</v>
       </c>
-      <c r="AC104" s="8"/>
+      <c r="AC104" s="8">
+        <v>7.4665559999999997</v>
+      </c>
       <c r="AD104" s="8">
         <v>15.781483333333334</v>
       </c>
@@ -13932,7 +14649,9 @@
       <c r="AB105" s="8">
         <v>18.785963157894734</v>
       </c>
-      <c r="AC105" s="8"/>
+      <c r="AC105" s="8">
+        <v>27.178820999999999</v>
+      </c>
       <c r="AD105" s="8">
         <v>32.166665000000002</v>
       </c>
@@ -14061,7 +14780,9 @@
       <c r="AB106" s="8">
         <v>2.0282608695652171</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>5.8525650000000002</v>
+      </c>
       <c r="AD106" s="8">
         <v>12.851447826086957</v>
       </c>
@@ -14190,7 +14911,9 @@
       <c r="AB107" s="8">
         <v>27.639742307692305</v>
       </c>
-      <c r="AC107" s="8"/>
+      <c r="AC107" s="8">
+        <v>34.459384999999997</v>
+      </c>
       <c r="AD107" s="8">
         <v>40.358025925925922</v>
       </c>
@@ -14410,7 +15133,9 @@
       <c r="AB109" s="8">
         <v>13.666666666666666</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>17.226851</v>
+      </c>
       <c r="AD109" s="8">
         <v>25.162038888888887</v>
       </c>
@@ -14632,7 +15357,9 @@
       <c r="AB111" s="8">
         <v>3.2000000000000002</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>7.5151510000000004</v>
+      </c>
       <c r="AD111" s="8">
         <v>14.4697</v>
       </c>
@@ -14852,7 +15579,9 @@
       <c r="AB113" s="8">
         <v>1.579310344827586</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="8">
+        <v>3.4654210000000001</v>
+      </c>
       <c r="AD113" s="8">
         <v>13.364368965517242</v>
       </c>
@@ -14981,7 +15710,9 @@
       <c r="AB114" s="8">
         <v>1.6871807692307692</v>
       </c>
-      <c r="AC114" s="8"/>
+      <c r="AC114" s="8">
+        <v>4.7056969999999998</v>
+      </c>
       <c r="AD114" s="8">
         <v>12.541359259259259</v>
       </c>
@@ -15110,7 +15841,9 @@
       <c r="AB115" s="8">
         <v>2.9909708333333334</v>
       </c>
-      <c r="AC115" s="8"/>
+      <c r="AC115" s="8">
+        <v>4.9421619999999997</v>
+      </c>
       <c r="AD115" s="8">
         <v>12.014285714285714</v>
       </c>
@@ -15332,7 +16065,9 @@
       <c r="AB117" s="8">
         <v>8.5594217391304355</v>
       </c>
-      <c r="AC117" s="8"/>
+      <c r="AC117" s="8">
+        <v>12.102012</v>
+      </c>
       <c r="AD117" s="8">
         <v>17.032714814814817</v>
       </c>
@@ -15461,7 +16196,9 @@
       <c r="AB118" s="8">
         <v>10.209877777777777</v>
       </c>
-      <c r="AC118" s="8"/>
+      <c r="AC118" s="8">
+        <v>14.967283</v>
+      </c>
       <c r="AD118" s="8">
         <v>21.91172962962963</v>
       </c>
@@ -15590,7 +16327,9 @@
       <c r="AB119" s="8">
         <v>3.2235294117647055</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>5.6941170000000003</v>
+      </c>
       <c r="AD119" s="8">
         <v>12.65</v>
       </c>
@@ -15717,7 +16456,9 @@
       <c r="AB120" s="8">
         <v>9.7388916666666656</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="8">
+        <v>13.836323</v>
+      </c>
       <c r="AD120" s="8">
         <v>21.940275</v>
       </c>
@@ -15844,7 +16585,9 @@
       <c r="AB121" s="8">
         <v>4.8666666666666663</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="8">
+        <v>9.8219989999999999</v>
+      </c>
       <c r="AD121" s="8">
         <v>17.591666666666665</v>
       </c>
@@ -15973,7 +16716,9 @@
       <c r="AB122" s="8">
         <v>3.7712136363636364</v>
       </c>
-      <c r="AC122" s="8"/>
+      <c r="AC122" s="8">
+        <v>7.1833330000000002</v>
+      </c>
       <c r="AD122" s="8">
         <v>14.133331818181817</v>
       </c>
@@ -16102,7 +16847,9 @@
       <c r="AB123" s="8">
         <v>5.9523000000000001</v>
       </c>
-      <c r="AC123" s="8"/>
+      <c r="AC123" s="8">
+        <v>8.5700749999999992</v>
+      </c>
       <c r="AD123" s="8">
         <v>16.468389655172412</v>
       </c>
@@ -16231,7 +16978,9 @@
       <c r="AB124" s="8">
         <v>6.2999999999999998</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>10.795833</v>
+      </c>
       <c r="AD124" s="8">
         <v>8.7083250000000003</v>
       </c>
@@ -16343,7 +17092,7 @@
         <v>0.07003769782377306</v>
       </c>
       <c r="W125" s="6">
-        <v>0.030031496777535575</v>
+        <v>0.031190411821311558</v>
       </c>
       <c r="X125" s="8">
         <v>23.282291666666666</v>
@@ -16360,7 +17109,9 @@
       <c r="AB125" s="8">
         <v>4.4281250000000005</v>
       </c>
-      <c r="AC125" s="8"/>
+      <c r="AC125" s="8">
+        <v>9.1885410000000007</v>
+      </c>
       <c r="AD125" s="8">
         <v>17.131597916666667</v>
       </c>
@@ -16411,7 +17162,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>44</v>
@@ -16447,25 +17198,61 @@
       <c t="s" r="N126" s="4">
         <v>52</v>
       </c>
-      <c r="O126" s="5"/>
-      <c r="P126" s="5"/>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
-      <c r="V126" s="6"/>
-      <c r="W126" s="6"/>
-      <c r="X126" s="8"/>
-      <c r="Y126" s="6"/>
-      <c r="Z126" s="6"/>
-      <c r="AA126" s="8"/>
-      <c r="AB126" s="8"/>
-      <c r="AC126" s="8"/>
-      <c r="AD126" s="8"/>
-      <c r="AE126" s="6"/>
+      <c r="O126" s="5">
+        <v>2482.1199999999999</v>
+      </c>
+      <c r="P126" s="5">
+        <v>2482.1199999999999</v>
+      </c>
+      <c r="Q126" s="6">
+        <v>-0.42177846939441099</v>
+      </c>
+      <c r="R126" s="7">
+        <v>31</v>
+      </c>
+      <c r="S126" s="6">
+        <v>-0.49180327868852458</v>
+      </c>
+      <c r="T126" s="6">
+        <v>0.00064904194801218313</v>
+      </c>
+      <c r="U126" s="6">
+        <v>-0.27588472757159205</v>
+      </c>
+      <c r="V126" s="6">
+        <v>0.17872222132693022</v>
+      </c>
+      <c r="W126" s="6">
+        <v>0.15952089342980999</v>
+      </c>
+      <c r="X126" s="8">
+        <v>37.169842857142854</v>
+      </c>
+      <c r="Y126" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z126" s="6">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="AA126" s="8">
+        <v>6.3171727272727276</v>
+      </c>
+      <c r="AB126" s="8">
+        <v>12.25087894736842</v>
+      </c>
+      <c r="AC126" s="8">
+        <v>17.927688</v>
+      </c>
+      <c r="AD126" s="8">
+        <v>23.730157142857145</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>0.38095238095238093</v>
+      </c>
       <c r="AF126" s="9"/>
-      <c r="AG126" s="5"/>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
       <c r="AH126" s="10">
         <v>2</v>
       </c>
@@ -16584,7 +17371,9 @@
       <c r="AB127" s="8">
         <v>14.217706250000001</v>
       </c>
-      <c r="AC127" s="8"/>
+      <c r="AC127" s="8">
+        <v>22.645833</v>
+      </c>
       <c r="AD127" s="8">
         <v>32.466668749999997</v>
       </c>
@@ -16713,7 +17502,9 @@
       <c r="AB128" s="8">
         <v>13.866666666666667</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="8">
+        <v>23.029166</v>
+      </c>
       <c r="AD128" s="8">
         <v>25.331250000000001</v>
       </c>
@@ -16842,7 +17633,9 @@
       <c r="AB129" s="8">
         <v>6.8833333333333329</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="8">
+        <v>13.087035999999999</v>
+      </c>
       <c r="AD129" s="8">
         <v>20.004937037037035</v>
       </c>
@@ -16971,7 +17764,9 @@
       <c r="AB130" s="8">
         <v>7.5657388888888892</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="8">
+        <v>9.4517039999999994</v>
+      </c>
       <c r="AD130" s="8">
         <v>15.630699999999999</v>
       </c>
@@ -17098,7 +17893,9 @@
       <c r="AB131" s="8">
         <v>25.75</v>
       </c>
-      <c r="AC131" s="8"/>
+      <c r="AC131" s="8">
+        <v>37.998148</v>
+      </c>
       <c r="AD131" s="8">
         <v>41.71875</v>
       </c>
@@ -17210,7 +18007,7 @@
         <v>0.022240127025190667</v>
       </c>
       <c r="W132" s="6">
-        <v>-0.022288936285142971</v>
+        <v>-0.022711626898625714</v>
       </c>
       <c r="X132" s="8">
         <v>26.847826086956523</v>
@@ -17227,7 +18024,9 @@
       <c r="AB132" s="8">
         <v>8.0701964705882343</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="8">
+        <v>12.675751</v>
+      </c>
       <c r="AD132" s="8">
         <v>17.779347826086958</v>
       </c>
@@ -17356,7 +18155,9 @@
       <c r="AB133" s="8">
         <v>16.989285714285714</v>
       </c>
-      <c r="AC133" s="8"/>
+      <c r="AC133" s="8">
+        <v>19.258980999999999</v>
+      </c>
       <c r="AD133" s="8">
         <v>21.266666666666666</v>
       </c>
@@ -17485,7 +18286,9 @@
       <c r="AB134" s="8">
         <v>17.732457894736843</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="8">
+        <v>24.827192</v>
+      </c>
       <c r="AD134" s="8">
         <v>32.070173684210523</v>
       </c>
@@ -17614,7 +18417,9 @@
       <c r="AB135" s="8">
         <v>4.678260869565217</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="8">
+        <v>8.2304329999999997</v>
+      </c>
       <c r="AD135" s="8">
         <v>15.190578260869566</v>
       </c>
@@ -17665,7 +18470,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>44</v>
@@ -17701,25 +18506,61 @@
       <c t="s" r="N136" s="4">
         <v>52</v>
       </c>
-      <c r="O136" s="5"/>
-      <c r="P136" s="5"/>
-      <c r="Q136" s="6"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="6"/>
-      <c r="T136" s="6"/>
-      <c r="U136" s="6"/>
-      <c r="V136" s="6"/>
-      <c r="W136" s="6"/>
-      <c r="X136" s="8"/>
-      <c r="Y136" s="6"/>
-      <c r="Z136" s="6"/>
-      <c r="AA136" s="8"/>
-      <c r="AB136" s="8"/>
-      <c r="AC136" s="8"/>
-      <c r="AD136" s="8"/>
-      <c r="AE136" s="6"/>
+      <c r="O136" s="5">
+        <v>3912.3000000000002</v>
+      </c>
+      <c r="P136" s="5">
+        <v>3912.3000000000002</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>-0.22923861628207076</v>
+      </c>
+      <c r="R136" s="7">
+        <v>41</v>
+      </c>
+      <c r="S136" s="6">
+        <v>-0.12765957446808507</v>
+      </c>
+      <c r="T136" s="6">
+        <v>0.27491276231372846</v>
+      </c>
+      <c r="U136" s="6">
+        <v>-0.0055309664391789996</v>
+      </c>
+      <c r="V136" s="6">
+        <v>0.01609309102062725</v>
+      </c>
+      <c r="W136" s="6">
+        <v>-0.0070825345704572757</v>
+      </c>
+      <c r="X136" s="8">
+        <v>35.458331250000001</v>
+      </c>
+      <c r="Y136" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z136" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="AA136" s="8">
+        <v>6.2416666666666663</v>
+      </c>
+      <c r="AB136" s="8">
+        <v>11.369793749999999</v>
+      </c>
+      <c r="AC136" s="8">
+        <v>18.754166000000001</v>
+      </c>
+      <c r="AD136" s="8">
+        <v>25.672918750000001</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>0.3125</v>
+      </c>
       <c r="AF136" s="9"/>
-      <c r="AG136" s="5"/>
+      <c r="AG136" s="5">
+        <v>-189.40000000000001</v>
+      </c>
       <c r="AH136" s="10">
         <v>2</v>
       </c>
@@ -17836,7 +18677,9 @@
       <c r="AB137" s="8">
         <v>7.4749999999999996</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="8">
+        <v>14.702776999999999</v>
+      </c>
       <c r="AD137" s="8">
         <v>21.308350000000001</v>
       </c>
@@ -17963,7 +18806,9 @@
       <c r="AB138" s="8">
         <v>5.4210626373626374</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="8">
+        <v>10.272674</v>
+      </c>
       <c r="AD138" s="8">
         <v>16.630496808510639</v>
       </c>
@@ -18014,7 +18859,7 @@
         <v>19790</v>
       </c>
       <c r="B139" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C139" s="4">
         <v>44</v>
@@ -18050,25 +18895,61 @@
       <c t="s" r="N139" s="4">
         <v>52</v>
       </c>
-      <c r="O139" s="5"/>
-      <c r="P139" s="5"/>
-      <c r="Q139" s="6"/>
-      <c r="R139" s="7"/>
-      <c r="S139" s="6"/>
-      <c r="T139" s="6"/>
-      <c r="U139" s="6"/>
-      <c r="V139" s="6"/>
-      <c r="W139" s="6"/>
-      <c r="X139" s="8"/>
-      <c r="Y139" s="6"/>
-      <c r="Z139" s="6"/>
-      <c r="AA139" s="8"/>
-      <c r="AB139" s="8"/>
-      <c r="AC139" s="8"/>
-      <c r="AD139" s="8"/>
-      <c r="AE139" s="6"/>
+      <c r="O139" s="5">
+        <v>4966.1000000000004</v>
+      </c>
+      <c r="P139" s="5">
+        <v>4966.1000000000004</v>
+      </c>
+      <c r="Q139" s="6">
+        <v>-0.29589027111790411</v>
+      </c>
+      <c r="R139" s="7">
+        <v>48</v>
+      </c>
+      <c r="S139" s="6">
+        <v>-0.34246575342465757</v>
+      </c>
+      <c r="T139" s="6">
+        <v>0</v>
+      </c>
+      <c r="U139" s="6">
+        <v>-0.26371800809488333</v>
+      </c>
+      <c r="V139" s="6">
+        <v>0.025400817542941139</v>
+      </c>
+      <c r="W139" s="6">
+        <v>-0.001157246128752945</v>
+      </c>
+      <c r="X139" s="8">
+        <v>17.308728571428571</v>
+      </c>
+      <c r="Y139" s="6">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="Z139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="8">
+        <v>2.5957446808510638</v>
+      </c>
+      <c r="AB139" s="8">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="AC139" s="8">
+        <v>5.2391259999999997</v>
+      </c>
+      <c r="AD139" s="8">
+        <v>12.020633333333333</v>
+      </c>
+      <c r="AE139" s="6">
+        <v>1</v>
+      </c>
       <c r="AF139" s="9"/>
-      <c r="AG139" s="5"/>
+      <c r="AG139" s="5">
+        <v>0</v>
+      </c>
       <c r="AH139" s="10">
         <v>5</v>
       </c>
@@ -18299,7 +19180,7 @@
         <v>19794</v>
       </c>
       <c r="B142" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C142" s="4">
         <v>44</v>
@@ -18333,25 +19214,61 @@
       <c t="s" r="N142" s="4">
         <v>52</v>
       </c>
-      <c r="O142" s="5"/>
-      <c r="P142" s="5"/>
-      <c r="Q142" s="6"/>
-      <c r="R142" s="7"/>
-      <c r="S142" s="6"/>
-      <c r="T142" s="6"/>
-      <c r="U142" s="6"/>
-      <c r="V142" s="6"/>
-      <c r="W142" s="6"/>
-      <c r="X142" s="8"/>
-      <c r="Y142" s="6"/>
-      <c r="Z142" s="6"/>
-      <c r="AA142" s="8"/>
-      <c r="AB142" s="8"/>
-      <c r="AC142" s="8"/>
-      <c r="AD142" s="8"/>
-      <c r="AE142" s="6"/>
+      <c r="O142" s="5">
+        <v>8306.7999999999993</v>
+      </c>
+      <c r="P142" s="5">
+        <v>8306.7999999999993</v>
+      </c>
+      <c r="Q142" s="6">
+        <v>0.18580652344904269</v>
+      </c>
+      <c r="R142" s="7">
+        <v>81</v>
+      </c>
+      <c r="S142" s="6">
+        <v>0.22727272727272729</v>
+      </c>
+      <c r="T142" s="6">
+        <v>0</v>
+      </c>
+      <c r="U142" s="6">
+        <v>-0.34105190927914486</v>
+      </c>
+      <c r="V142" s="6">
+        <v>0.034434439254586606</v>
+      </c>
+      <c r="W142" s="6">
+        <v>0.010007463764626572</v>
+      </c>
+      <c r="X142" s="8">
+        <v>31.605797826086956</v>
+      </c>
+      <c r="Y142" s="6">
+        <v>0.47826086956521741</v>
+      </c>
+      <c r="Z142" s="6">
+        <v>0.10869565217391304</v>
+      </c>
+      <c r="AA142" s="8">
+        <v>5.9845385542168676</v>
+      </c>
+      <c r="AB142" s="8">
+        <v>9.3217046511627917</v>
+      </c>
+      <c r="AC142" s="8">
+        <v>15.232574</v>
+      </c>
+      <c r="AD142" s="8">
+        <v>23.317391304347826</v>
+      </c>
+      <c r="AE142" s="6">
+        <v>0.39130434782608697</v>
+      </c>
       <c r="AF142" s="9"/>
-      <c r="AG142" s="5"/>
+      <c r="AG142" s="5">
+        <v>470</v>
+      </c>
       <c r="AH142" s="10">
         <v>2</v>
       </c>
@@ -18468,7 +19385,9 @@
       <c r="AB143" s="8">
         <v>8.9787499999999998</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="8">
+        <v>15.001098000000001</v>
+      </c>
       <c r="AD143" s="8">
         <v>21.805813953488371</v>
       </c>
@@ -18597,7 +19516,9 @@
       <c r="AB144" s="8">
         <v>2.4117953846153846</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="8">
+        <v>4.2301510000000002</v>
+      </c>
       <c r="AD144" s="8">
         <v>11.051010606060606</v>
       </c>
@@ -18726,7 +19647,9 @@
       <c r="AB145" s="8">
         <v>1.6526679999999998</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>7.4890290000000004</v>
+      </c>
       <c r="AD145" s="8">
         <v>12.977778787878789</v>
       </c>
@@ -18855,7 +19778,9 @@
       <c r="AB146" s="8">
         <v>4.1734119047619043</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>8.6617840000000008</v>
+      </c>
       <c r="AD146" s="8">
         <v>14.49325476190476</v>
       </c>
@@ -18984,7 +19909,9 @@
       <c r="AB147" s="8">
         <v>3.07027027027027</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="8">
+        <v>7.0657649999999999</v>
+      </c>
       <c r="AD147" s="8">
         <v>14.021170270270272</v>
       </c>
@@ -19115,7 +20042,9 @@
       <c r="AB148" s="8">
         <v>12.471318604651163</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="8">
+        <v>18.833438000000001</v>
+      </c>
       <c r="AD148" s="8">
         <v>26.421590909090909</v>
       </c>
@@ -19244,7 +20173,9 @@
       <c r="AB149" s="8">
         <v>10.969842857142858</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>16.270565000000001</v>
+      </c>
       <c r="AD149" s="8">
         <v>23.313490476190477</v>
       </c>
@@ -19371,7 +20302,9 @@
       <c r="AB150" s="8">
         <v>6.9683896551724143</v>
       </c>
-      <c r="AC150" s="8"/>
+      <c r="AC150" s="8">
+        <v>10.48678</v>
+      </c>
       <c r="AD150" s="8">
         <v>17.430458620689656</v>
       </c>
@@ -19599,7 +20532,9 @@
       <c r="AB152" s="8">
         <v>3.6993576923076925</v>
       </c>
-      <c r="AC152" s="8"/>
+      <c r="AC152" s="8">
+        <v>7.2666649999999997</v>
+      </c>
       <c r="AD152" s="8">
         <v>14.206411538461538</v>
       </c>
@@ -19728,7 +20663,9 @@
       <c r="AB153" s="8">
         <v>11.659523214285715</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>15.916069999999999</v>
+      </c>
       <c r="AD153" s="8">
         <v>23.852083928571428</v>
       </c>
@@ -19857,7 +20794,9 @@
       <c r="AB154" s="8">
         <v>6.8897461538461533</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>8.5861710000000002</v>
+      </c>
       <c r="AD154" s="8">
         <v>16.838092857142858</v>
       </c>
@@ -19984,7 +20923,9 @@
       <c r="AB155" s="8">
         <v>3.8670061224489798</v>
       </c>
-      <c r="AC155" s="8"/>
+      <c r="AC155" s="8">
+        <v>6.1360530000000004</v>
+      </c>
       <c r="AD155" s="8">
         <v>12.195577551020408</v>
       </c>
@@ -20113,7 +21054,9 @@
       <c r="AB156" s="8">
         <v>4.4454545454545453</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>10.867171000000001</v>
+      </c>
       <c r="AD156" s="8">
         <v>17.798990909090911</v>
       </c>
@@ -20432,7 +21375,9 @@
       <c r="AB159" s="8">
         <v>5.0507928571428566</v>
       </c>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="8">
+        <v>10.531025</v>
+      </c>
       <c r="AD159" s="8">
         <v>17.299225581395351</v>
       </c>
@@ -20540,7 +21485,7 @@
         <v>0.062894090373229183</v>
       </c>
       <c r="W160" s="6">
-        <v>0.010525431877605591</v>
+        <v>0.010140150292748146</v>
       </c>
       <c r="X160" s="8">
         <v>38.059877777777778</v>
@@ -20557,7 +21502,9 @@
       <c r="AB160" s="8">
         <v>12.798766666666667</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>19.958288</v>
+      </c>
       <c r="AD160" s="8">
         <v>26.856788888888886</v>
       </c>
@@ -20684,7 +21631,9 @@
       <c r="AB161" s="8">
         <v>1.83335</v>
       </c>
-      <c r="AC161" s="8"/>
+      <c r="AC161" s="8">
+        <v>3.0333329999999998</v>
+      </c>
       <c r="AD161" s="8">
         <v>8.3083500000000008</v>
       </c>
@@ -20735,7 +21684,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20771,25 +21720,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>3103.0799999999999</v>
+      </c>
+      <c r="P162" s="5">
+        <v>3103.0799999999999</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.29489556634127723</v>
+      </c>
+      <c r="R162" s="7">
+        <v>36</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.45454545454545459</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.31790340564858138</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.02636422522139294</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.018386731892184541</v>
+      </c>
+      <c r="W162" s="6">
+        <v>-0.0038073462495327227</v>
+      </c>
+      <c r="X162" s="8">
+        <v>21.609375</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>3.2130218749999999</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>4.6369071428571429</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>8.8244039999999995</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>15.751043749999999</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.9375</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-166.72999999999999</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -20908,7 +21893,9 @@
       <c r="AB163" s="8">
         <v>11.321171621621621</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>17.272252999999999</v>
+      </c>
       <c r="AD163" s="8">
         <v>24.57987012987013</v>
       </c>
@@ -21037,7 +22024,9 @@
       <c r="AB164" s="8">
         <v>8.5972222222222214</v>
       </c>
-      <c r="AC164" s="8"/>
+      <c r="AC164" s="8">
+        <v>12.466269</v>
+      </c>
       <c r="AD164" s="8">
         <v>17.441271428571429</v>
       </c>
@@ -21261,7 +22250,9 @@
       <c r="AB166" s="8">
         <v>9.4289473684210527</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>17.884502000000001</v>
+      </c>
       <c r="AD166" s="8">
         <v>24.382457894736842</v>
       </c>
@@ -21390,7 +22381,9 @@
       <c r="AB167" s="8">
         <v>9.0123195652173926</v>
       </c>
-      <c r="AC167" s="8"/>
+      <c r="AC167" s="8">
+        <v>12.772040000000001</v>
+      </c>
       <c r="AD167" s="8">
         <v>18.578125</v>
       </c>
@@ -21519,7 +22512,9 @@
       <c r="AB168" s="8">
         <v>3.8304586206896549</v>
       </c>
-      <c r="AC168" s="8"/>
+      <c r="AC168" s="8">
+        <v>7.1798840000000004</v>
+      </c>
       <c r="AD168" s="8">
         <v>14.11321724137931</v>
       </c>
@@ -21648,7 +22643,9 @@
       <c r="AB169" s="8">
         <v>16.280862962962964</v>
       </c>
-      <c r="AC169" s="8"/>
+      <c r="AC169" s="8">
+        <v>29.465387</v>
+      </c>
       <c r="AD169" s="8">
         <v>35.709524999999999</v>
       </c>
@@ -21777,7 +22774,9 @@
       <c r="AB170" s="8">
         <v>2.6096473684210526</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>7.0078940000000003</v>
+      </c>
       <c r="AD170" s="8">
         <v>13.960526315789474</v>
       </c>
@@ -21906,7 +22905,9 @@
       <c r="AB171" s="8">
         <v>2.8220000000000001</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>8.0702750000000005</v>
+      </c>
       <c r="AD171" s="8">
         <v>14.21551724137931</v>
       </c>
@@ -21957,7 +22958,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>44</v>
@@ -21993,25 +22994,61 @@
       <c t="s" r="N172" s="4">
         <v>52</v>
       </c>
-      <c r="O172" s="5"/>
-      <c r="P172" s="5"/>
-      <c r="Q172" s="6"/>
-      <c r="R172" s="7"/>
-      <c r="S172" s="6"/>
-      <c r="T172" s="6"/>
-      <c r="U172" s="6"/>
-      <c r="V172" s="6"/>
-      <c r="W172" s="6"/>
-      <c r="X172" s="8"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="6"/>
-      <c r="AA172" s="8"/>
-      <c r="AB172" s="8"/>
-      <c r="AC172" s="8"/>
-      <c r="AD172" s="8"/>
-      <c r="AE172" s="6"/>
+      <c r="O172" s="5">
+        <v>1722.28</v>
+      </c>
+      <c r="P172" s="5">
+        <v>1722.28</v>
+      </c>
+      <c r="Q172" s="6">
+        <v>0.1513644325003678</v>
+      </c>
+      <c r="R172" s="7">
+        <v>21</v>
+      </c>
+      <c r="S172" s="6">
+        <v>0.050000000000000044</v>
+      </c>
+      <c r="T172" s="6">
+        <v>0.32227692361288524</v>
+      </c>
+      <c r="U172" s="6">
+        <v>0.0037863181364238101</v>
+      </c>
+      <c r="V172" s="6">
+        <v>0.18648274380472396</v>
+      </c>
+      <c r="W172" s="6">
+        <v>0.10822020809624452</v>
+      </c>
+      <c r="X172" s="8">
+        <v>17.693857894736841</v>
+      </c>
+      <c r="Y172" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="8">
+        <v>3.8769857142857145</v>
+      </c>
+      <c r="AB172" s="8">
+        <v>2.7314833333333333</v>
+      </c>
+      <c r="AC172" s="8">
+        <v>6.6727090000000002</v>
+      </c>
+      <c r="AD172" s="8">
+        <v>13.273684210526316</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>0.89473684210526316</v>
+      </c>
       <c r="AF172" s="9"/>
-      <c r="AG172" s="5"/>
+      <c r="AG172" s="5">
+        <v>0</v>
+      </c>
       <c r="AH172" s="10">
         <v>1</v>
       </c>
@@ -22130,7 +23167,9 @@
       <c r="AB173" s="8">
         <v>4.2583333333333337</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>19.657406999999999</v>
+      </c>
       <c r="AD173" s="8">
         <v>20.414816666666667</v>
       </c>
@@ -22259,7 +23298,9 @@
       <c r="AB174" s="8">
         <v>3.5496116279069767</v>
       </c>
-      <c r="AC174" s="8"/>
+      <c r="AC174" s="8">
+        <v>10.163565</v>
+      </c>
       <c r="AD174" s="8">
         <v>17.117830232558138</v>
       </c>
@@ -22310,7 +23351,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -22346,25 +23387,61 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
-      <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="O175" s="5">
+        <v>2687.3000000000002</v>
+      </c>
+      <c r="P175" s="5">
+        <v>2687.3000000000002</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>0.23568794430598627</v>
+      </c>
+      <c r="R175" s="7">
+        <v>41</v>
+      </c>
+      <c r="S175" s="6">
+        <v>0.13888888888888884</v>
+      </c>
+      <c r="T175" s="6">
+        <v>0.28786990659770029</v>
+      </c>
+      <c r="U175" s="6">
+        <v>-0.077187958173631527</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.029744911249209239</v>
+      </c>
+      <c r="W175" s="6">
+        <v>-0.017607449856733522</v>
+      </c>
+      <c r="X175" s="8">
+        <v>25.846665000000002</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>4.515657575757575</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>3.1975000000000002</v>
+      </c>
+      <c r="AC175" s="8">
+        <v>8.0325000000000006</v>
+      </c>
+      <c r="AD175" s="8">
+        <v>14.994999999999999</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-0.90000000000000002</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -22481,7 +23558,9 @@
       <c r="AB176" s="8">
         <v>8.206669999999999</v>
       </c>
-      <c r="AC176" s="8"/>
+      <c r="AC176" s="8">
+        <v>10.703332</v>
+      </c>
       <c r="AD176" s="8">
         <v>17.66</v>
       </c>
@@ -22610,7 +23689,9 @@
       <c r="AB177" s="8">
         <v>1.1468750000000001</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>4.1500000000000004</v>
+      </c>
       <c r="AD177" s="8">
         <v>11.09583125</v>
       </c>
@@ -22739,7 +23820,9 @@
       <c r="AB178" s="8">
         <v>3.3623645161290323</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>8.6456979999999994</v>
+      </c>
       <c r="AD178" s="8">
         <v>15.600538709677419</v>
       </c>
@@ -22866,7 +23949,9 @@
       <c r="AB179" s="8">
         <v>1.1821827586206894</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>5.4557460000000004</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.40574827586207</v>
       </c>
@@ -22993,7 +24078,9 @@
       <c r="AB180" s="8">
         <v>2.5033400000000001</v>
       </c>
-      <c r="AC180" s="8"/>
+      <c r="AC180" s="8">
+        <v>6.3966659999999997</v>
+      </c>
       <c r="AD180" s="8">
         <v>14.36666</v>
       </c>
@@ -23044,7 +24131,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -23080,25 +24167,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>2820.8800000000001</v>
+      </c>
+      <c r="P181" s="5">
+        <v>2820.8800000000001</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.40388386236276608</v>
+      </c>
+      <c r="R181" s="7">
+        <v>30</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="T181" s="6">
+        <v>-0.067159893366608991</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.34673931539094183</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.10952114233856103</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.072227815433481751</v>
+      </c>
+      <c r="X181" s="8">
+        <v>17.028207692307692</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>4.9637931034482756</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>0.90555555555555556</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>5.6260669999999999</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>12.817946153846153</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23200,7 +24323,7 @@
         <v>0.10904582184869994</v>
       </c>
       <c r="W182" s="6">
-        <v>0.084768508032134426</v>
+        <v>0.084424336734843966</v>
       </c>
       <c r="X182" s="8">
         <v>24.370238095238093</v>
@@ -23217,7 +24340,9 @@
       <c r="AB182" s="8">
         <v>5.1452371428571428</v>
       </c>
-      <c r="AC182" s="8"/>
+      <c r="AC182" s="8">
+        <v>9.8537649999999992</v>
+      </c>
       <c r="AD182" s="8">
         <v>16.41269761904762</v>
       </c>
@@ -23346,7 +24471,9 @@
       <c r="AB183" s="8">
         <v>2.9455115384615382</v>
       </c>
-      <c r="AC183" s="8"/>
+      <c r="AC183" s="8">
+        <v>9.6562260000000002</v>
+      </c>
       <c r="AD183" s="8">
         <v>16.997617857142856</v>
       </c>
@@ -23475,7 +24602,9 @@
       <c r="AB184" s="8">
         <v>9.7890625</v>
       </c>
-      <c r="AC184" s="8"/>
+      <c r="AC184" s="8">
+        <v>17.002296999999999</v>
+      </c>
       <c r="AD184" s="8">
         <v>25.198529411764707</v>
       </c>
@@ -23697,7 +24826,9 @@
       <c r="AB186" s="8">
         <v>10.64743846153846</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>16.987435000000001</v>
+      </c>
       <c r="AD186" s="8">
         <v>22.748807142857142</v>
       </c>
@@ -23748,7 +24879,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23784,25 +24915,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>1119.5999999999999</v>
+      </c>
+      <c r="P187" s="5">
+        <v>1119.5999999999999</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.30242121397151378</v>
+      </c>
+      <c r="R187" s="7">
+        <v>13</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.47999999999999998</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.37466059306895327</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.20176580921757772</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.063939799928545912</v>
+      </c>
+      <c r="X187" s="8">
+        <v>45.388888888888886</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>12.289285714285715</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>10.038888888888888</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>20.575925000000002</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>27.538888888888888</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.22222222222222221</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-115.59999999999999</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -23923,7 +25090,9 @@
       <c r="AB188" s="8">
         <v>8.6808350000000001</v>
       </c>
-      <c r="AC188" s="8"/>
+      <c r="AC188" s="8">
+        <v>12.553333</v>
+      </c>
       <c r="AD188" s="8">
         <v>19.520834999999998</v>
       </c>
@@ -23974,7 +25143,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -24010,25 +25179,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>5123.29</v>
+      </c>
+      <c r="P189" s="5">
+        <v>5123.29</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.61228388185016658</v>
+      </c>
+      <c r="R189" s="7">
+        <v>70</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.22807017543859653</v>
+      </c>
+      <c r="T189" s="6">
+        <v>2.8126572963857206</v>
+      </c>
+      <c r="U189" s="6">
+        <v>2.5245475075586197</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.066347015296811238</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.037800905277663374</v>
+      </c>
+      <c r="X189" s="8">
+        <v>33.364166666666662</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>5.2019042857142859</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>17.332703773584903</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>22.363814999999999</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>26.688333333333333</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.45000000000000001</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -24069,7 +25274,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24105,25 +25310,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>3001.1900000000001</v>
+      </c>
+      <c r="P190" s="5">
+        <v>3001.1900000000001</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.23141005941405457</v>
+      </c>
+      <c r="R190" s="7">
+        <v>35</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.39655172413793105</v>
+      </c>
+      <c r="T190" s="6">
+        <v>1.9054654320452888</v>
+      </c>
+      <c r="U190" s="6">
+        <v>1.4331227946247989</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.07345636230961719</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.039566471966120106</v>
+      </c>
+      <c r="X190" s="8">
+        <v>23.424245454545453</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>4.0151970588235288</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>5.9033299999999995</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>10.823029</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>17.12879090909091</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.81818181818181823</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-157.80000000000001</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24242,7 +25483,9 @@
       <c r="AB191" s="8">
         <v>3.471111111111111</v>
       </c>
-      <c r="AC191" s="8"/>
+      <c r="AC191" s="8">
+        <v>8.0101180000000003</v>
+      </c>
       <c r="AD191" s="8">
         <v>14.747517021276595</v>
       </c>
@@ -24369,7 +25612,9 @@
       <c r="AB192" s="8">
         <v>5.9428571428571431</v>
       </c>
-      <c r="AC192" s="8"/>
+      <c r="AC192" s="8">
+        <v>9.824999</v>
+      </c>
       <c r="AD192" s="8">
         <v>16.776192857142856</v>
       </c>
@@ -24496,7 +25741,9 @@
       <c r="AB193" s="8">
         <v>18.494117647058822</v>
       </c>
-      <c r="AC193" s="8"/>
+      <c r="AC193" s="8">
+        <v>25.238561000000001</v>
+      </c>
       <c r="AD193" s="8">
         <v>29.74648947368421</v>
       </c>
@@ -24627,7 +25874,9 @@
       <c r="AB194" s="8">
         <v>5.3845214285714293</v>
       </c>
-      <c r="AC194" s="8"/>
+      <c r="AC194" s="8">
+        <v>10.926745</v>
+      </c>
       <c r="AD194" s="8">
         <v>18.004764285714284</v>
       </c>
@@ -24678,7 +25927,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -24714,25 +25963,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>4373.6400000000003</v>
+      </c>
+      <c r="P195" s="5">
+        <v>4373.6400000000003</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>-0.1358082261072997</v>
+      </c>
+      <c r="R195" s="7">
+        <v>45</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.26229508196721307</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.33006482014980659</v>
+      </c>
+      <c r="U195" s="6">
+        <v>0.0031380497709002112</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.026875554458071535</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-9.7401706587647806E-05</v>
+      </c>
+      <c r="X195" s="8">
+        <v>34.713888888888889</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>6.042064285714285</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>13.106944444444444</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>26.136111111111109</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>0</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
@@ -24851,7 +26134,9 @@
       <c r="AB196" s="8">
         <v>29.501670000000001</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>40.464998999999999</v>
+      </c>
       <c r="AD196" s="8">
         <v>47.43</v>
       </c>
@@ -24980,7 +26265,9 @@
       <c r="AB197" s="8">
         <v>5.9287588235294111</v>
       </c>
-      <c r="AC197" s="8"/>
+      <c r="AC197" s="8">
+        <v>8.8787579999999995</v>
+      </c>
       <c r="AD197" s="8">
         <v>15.561859615384614</v>
       </c>
@@ -25109,7 +26396,9 @@
       <c r="AB198" s="8">
         <v>41.595372222222217</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>61.883332000000003</v>
+      </c>
       <c r="AD198" s="8">
         <v>68.744444444444454</v>
       </c>
@@ -25238,7 +26527,9 @@
       <c r="AB199" s="8">
         <v>3.2488866666666665</v>
       </c>
-      <c r="AC199" s="8"/>
+      <c r="AC199" s="8">
+        <v>8.3755539999999993</v>
+      </c>
       <c r="AD199" s="8">
         <v>15.331113333333333</v>
       </c>
@@ -25289,7 +26580,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25325,25 +26616,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>1397.2</v>
+      </c>
+      <c r="P200" s="5">
+        <v>1397.2</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>0.70602456714449691</v>
+      </c>
+      <c r="R200" s="7">
+        <v>17</v>
+      </c>
+      <c r="S200" s="6">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0.27285005725737188</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.083362367592327513</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.16171163756083595</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.086418193529916976</v>
+      </c>
+      <c r="X200" s="8">
+        <v>28.538330000000002</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>9.1294117647058819</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>3.0574111111111111</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>13.515739999999999</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>19.551669999999998</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.69999999999999996</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-80</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25555,7 +26882,9 @@
       <c r="AB202" s="8">
         <v>4.7153846153846155</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>10.429486000000001</v>
+      </c>
       <c r="AD202" s="8">
         <v>17.383330769230771</v>
       </c>
@@ -25751,10 +27080,10 @@
         <v>-0.4285714285714286</v>
       </c>
       <c r="T204" s="6">
-        <v>0.44809190540280713</v>
+        <v>0.4881457412036147</v>
       </c>
       <c r="U204" s="6">
-        <v>0.12151624687560084</v>
+        <v>0.16157008267640838</v>
       </c>
       <c r="V204" s="6">
         <v>0.039076716016150738</v>
@@ -25777,7 +27106,9 @@
       <c r="AB204" s="8">
         <v>18.524446666666666</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>26.478888000000001</v>
+      </c>
       <c r="AD204" s="8">
         <v>33.38666666666667</v>
       </c>
@@ -25902,7 +27233,9 @@
       <c r="AB205" s="8">
         <v>0.80833333333333324</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>5.4369040000000002</v>
+      </c>
       <c r="AD205" s="8">
         <v>12.477783333333333</v>
       </c>
@@ -26027,7 +27360,9 @@
       <c r="AB206" s="8">
         <v>8.0383300000000002</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>16.289999000000002</v>
+      </c>
       <c r="AD206" s="8">
         <v>23.20833</v>
       </c>
@@ -26152,7 +27487,9 @@
       <c r="AB207" s="8">
         <v>5.324361538461539</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>11.060072</v>
+      </c>
       <c r="AD207" s="8">
         <v>17.388092857142858</v>
       </c>
@@ -26277,7 +27614,9 @@
       <c r="AB208" s="8">
         <v>4.3011133333333333</v>
       </c>
-      <c r="AC208" s="8"/>
+      <c r="AC208" s="8">
+        <v>11.431666</v>
+      </c>
       <c r="AD208" s="8">
         <v>18.91778</v>
       </c>
@@ -26586,7 +27925,9 @@
       <c r="AB211" s="8">
         <v>7.0992047619047627</v>
       </c>
-      <c r="AC211" s="8"/>
+      <c r="AC211" s="8">
+        <v>13.915872</v>
+      </c>
       <c r="AD211" s="8">
         <v>20.432577272727272</v>
       </c>
@@ -27061,22 +28402,24 @@
       <c t="s" r="AB216" s="14">
         <v>315</v>
       </c>
-      <c r="AC216" s="14"/>
+      <c t="s" r="AC216" s="14">
+        <v>316</v>
+      </c>
       <c t="s" r="AD216" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -27086,10 +28429,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
@@ -912,66 +912,66 @@
   </si>
   <si>
     <t>214
-172</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 846.777,66</t>
-  </si>
-  <si>
-    <t>R$ 4.627,20
-R$ 4.731,05</t>
-  </si>
-  <si>
-    <t>3.2%
-5.5%</t>
+176</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 865.135,33</t>
+  </si>
+  <si>
+    <t>R$ 4.626,39
+R$ 4.727,83</t>
+  </si>
+  <si>
+    <t>2.8%
+5.1%</t>
   </si>
   <si>
     <t>50.5</t>
   </si>
   <si>
-    <t>(3.7%)</t>
-  </si>
-  <si>
-    <t>84.2%</t>
-  </si>
-  <si>
-    <t>35.1%</t>
+    <t>(3.9%)</t>
+  </si>
+  <si>
+    <t>82.8%</t>
+  </si>
+  <si>
+    <t>34.1%</t>
   </si>
   <si>
     <t>3.6%</t>
   </si>
   <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>27.1</t>
-  </si>
-  <si>
-    <t>72.4%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>72.7%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
   </si>
   <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>7.4</t>
+    <t>7.3</t>
   </si>
   <si>
     <t>12.3</t>
   </si>
   <si>
-    <t>19.0</t>
-  </si>
-  <si>
-    <t>71.7%</t>
-  </si>
-  <si>
-    <t>-R$ 16.837,31</t>
+    <t>18.9</t>
+  </si>
+  <si>
+    <t>72.0%</t>
+  </si>
+  <si>
+    <t>-R$ 18.055,95</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>7323.6000000000004</v>
+      </c>
+      <c r="P6" s="5">
+        <v>7323.6000000000004</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-0.16734220534480904</v>
+      </c>
+      <c r="R6" s="7">
+        <v>83</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.11702127659574468</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.32496509913157462</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.014447047899939921</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.041315719045278275</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0050207275110601335</v>
+      </c>
+      <c r="X6" s="8">
+        <v>22.016666153846153</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.93846153846153846</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>7.7148590361445786</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.0346153846153845</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>9.3307680000000008</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>16.290512307692307</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.83076923076923082</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4874,7 +4910,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4910,25 +4946,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>5191.2399999999998</v>
+      </c>
+      <c r="P28" s="5">
+        <v>5191.2399999999998</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.015993674552599701</v>
+      </c>
+      <c r="R28" s="7">
+        <v>53</v>
+      </c>
+      <c r="S28" s="6">
+        <v>-0.070175438596491224</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.0001811127977130705</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.32701624274739755</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.079523774666553665</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.070342923848637315</v>
+      </c>
+      <c r="X28" s="8">
+        <v>22.710257692307689</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>2.2880509433962266</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>5.9461538461538463</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>8.4653829999999992</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>15.384615384615385</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.88461538461538458</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-1218.6400000000001</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -5928,7 +6000,9 @@
       <c r="AB36" s="8">
         <v>9.0733333333333324</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>14.796666</v>
+      </c>
       <c r="AD36" s="8">
         <v>21.751113333333333</v>
       </c>
@@ -7883,7 +7957,9 @@
       <c r="AB51" s="8">
         <v>5.5499999999999998</v>
       </c>
-      <c r="AC51" s="8"/>
+      <c r="AC51" s="8">
+        <v>8.5066659999999992</v>
+      </c>
       <c r="AD51" s="8">
         <v>14.073339999999998</v>
       </c>
@@ -10077,7 +10153,7 @@
         <v>19647</v>
       </c>
       <c r="B69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C69" s="4">
         <v>44</v>
@@ -10111,25 +10187,61 @@
       <c t="s" r="N69" s="4">
         <v>52</v>
       </c>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="6"/>
-      <c r="T69" s="6"/>
-      <c r="U69" s="6"/>
-      <c r="V69" s="6"/>
-      <c r="W69" s="6"/>
-      <c r="X69" s="8"/>
-      <c r="Y69" s="6"/>
-      <c r="Z69" s="6"/>
-      <c r="AA69" s="8"/>
-      <c r="AB69" s="8"/>
-      <c r="AC69" s="8"/>
-      <c r="AD69" s="8"/>
-      <c r="AE69" s="6"/>
+      <c r="O69" s="5">
+        <v>3226.1399999999999</v>
+      </c>
+      <c r="P69" s="5">
+        <v>3226.1399999999999</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>0.12654780112719743</v>
+      </c>
+      <c r="R69" s="7">
+        <v>39</v>
+      </c>
+      <c r="S69" s="6">
+        <v>0.18181818181818188</v>
+      </c>
+      <c r="T69" s="6">
+        <v>0.0080901634770964691</v>
+      </c>
+      <c r="U69" s="6">
+        <v>-0.28943877203097201</v>
+      </c>
+      <c r="V69" s="6">
+        <v>0.034030296267365957</v>
+      </c>
+      <c r="W69" s="6">
+        <v>-0.022920115060102785</v>
+      </c>
+      <c r="X69" s="8">
+        <v>24.520369444444444</v>
+      </c>
+      <c r="Y69" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z69" s="6">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="AA69" s="8">
+        <v>2.8401717948717948</v>
+      </c>
+      <c r="AB69" s="8">
+        <v>4.8634250000000003</v>
+      </c>
+      <c r="AC69" s="8">
+        <v>7.7513870000000002</v>
+      </c>
+      <c r="AD69" s="8">
+        <v>15.712963888888888</v>
+      </c>
+      <c r="AE69" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF69" s="9"/>
-      <c r="AG69" s="5"/>
+      <c r="AG69" s="5">
+        <v>0</v>
+      </c>
       <c r="AH69" s="10">
         <v>2</v>
       </c>
@@ -10986,7 +11098,9 @@
       <c r="AB76" s="8">
         <v>4.1769833333333333</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>7.1016360000000001</v>
+      </c>
       <c r="AD76" s="8">
         <v>15.428014893617021</v>
       </c>
@@ -14260,7 +14374,9 @@
       <c r="AB102" s="8">
         <v>37.454165000000003</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>44.971589999999999</v>
+      </c>
       <c r="AD102" s="8">
         <v>49.75</v>
       </c>
@@ -21202,7 +21318,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21238,25 +21354,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2616.6900000000001</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2616.6900000000001</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.27712550830975957</v>
+      </c>
+      <c r="R158" s="7">
+        <v>24</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.40000000000000002</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.27919237662848867</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.017155299252108579</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.040397410468951227</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.0066811506139435707</v>
+      </c>
+      <c r="X158" s="8">
+        <v>24.759164999999999</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>5.0376826086956523</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>1.9091650000000002</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>7.4733320000000001</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>14.422499999999999</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.84999999999999998</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
@@ -911,55 +911,58 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-176</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 865.135,33</t>
-  </si>
-  <si>
-    <t>R$ 4.626,39
-R$ 4.727,83</t>
-  </si>
-  <si>
-    <t>2.8%
-5.1%</t>
-  </si>
-  <si>
-    <t>50.5</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+177</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 869.036,46</t>
+  </si>
+  <si>
+    <t>R$ 4.622,53
+R$ 4.723,16</t>
+  </si>
+  <si>
+    <t>2.3%
+5.4%</t>
+  </si>
+  <si>
+    <t>50.6</t>
   </si>
   <si>
     <t>(3.9%)</t>
   </si>
   <si>
-    <t>82.8%</t>
-  </si>
-  <si>
-    <t>34.1%</t>
+    <t>82.6%</t>
+  </si>
+  <si>
+    <t>33.9%</t>
   </si>
   <si>
     <t>3.6%</t>
   </si>
   <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>72.7%</t>
-  </si>
-  <si>
-    <t>10.1%</t>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>26.9</t>
+  </si>
+  <si>
+    <t>72.9%</t>
+  </si>
+  <si>
+    <t>10.0%</t>
   </si>
   <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>7.3</t>
+    <t>7.2</t>
   </si>
   <si>
     <t>12.3</t>
@@ -968,10 +971,10 @@
     <t>18.9</t>
   </si>
   <si>
-    <t>72.0%</t>
-  </si>
-  <si>
-    <t>-R$ 18.055,95</t>
+    <t>72.2%</t>
+  </si>
+  <si>
+    <t>-R$ 18.122,85</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1411,7 +1414,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="6.86" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -2249,10 +2252,10 @@
         <v>-0.07999999999999996</v>
       </c>
       <c r="T7" s="6">
-        <v>0.32741686902299366</v>
+        <v>0.30642856072188746</v>
       </c>
       <c r="U7" s="6">
-        <v>0.0058591749857601107</v>
+        <v>-0.015129133315346106</v>
       </c>
       <c r="V7" s="6">
         <v>0.036669964325329013</v>
@@ -5692,7 +5695,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5728,25 +5731,53 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
+      <c r="O34" s="5">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R34" s="7">
+        <v>73</v>
+      </c>
+      <c r="S34" s="6">
+        <v>-0.31132075471698117</v>
+      </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
       <c r="V34" s="6"/>
       <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="X34" s="8">
+        <v>23.89777777777778</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>7.9550930555555555</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.362962222222222</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>11.476295</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>17.37851777777778</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -16058,7 +16089,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>10.087878</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19199,7 +19232,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19235,25 +19268,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>3901.1300000000001</v>
+      </c>
+      <c r="P141" s="5">
+        <v>3901.1300000000001</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>1.558755624352298</v>
+      </c>
+      <c r="R141" s="7">
+        <v>48</v>
+      </c>
+      <c r="S141" s="6">
+        <v>1.5263157894736841</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.25146444748060176</v>
+      </c>
+      <c r="U141" s="6">
+        <v>-0.04651075457623817</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.097415748770228114</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.045853765447447271</v>
+      </c>
+      <c r="X141" s="8">
+        <v>18.582408333333333</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>2.8735500000000003</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>2.2152777777777777</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>4.9263880000000002</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>12.872686111111111</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.94444444444444442</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>-66.900000000000006</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -26157,7 +26226,9 @@
       <c r="AB195" s="8">
         <v>13.106944444444444</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>19.216666</v>
+      </c>
       <c r="AD195" s="8">
         <v>26.136111111111109</v>
       </c>
@@ -28491,112 +28562,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
@@ -915,66 +915,66 @@
   </si>
   <si>
     <t>215
-177</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>R$ 869.036,46</t>
-  </si>
-  <si>
-    <t>R$ 4.622,53
-R$ 4.723,16</t>
-  </si>
-  <si>
-    <t>2.3%
-5.4%</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>(3.9%)</t>
-  </si>
-  <si>
-    <t>82.6%</t>
-  </si>
-  <si>
-    <t>33.9%</t>
+179</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>R$ 879.913,10</t>
+  </si>
+  <si>
+    <t>R$ 4.631,12
+R$ 4.731,15</t>
+  </si>
+  <si>
+    <t>2.2%
+5.2%</t>
+  </si>
+  <si>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>(4.1%)</t>
+  </si>
+  <si>
+    <t>78.3%</t>
+  </si>
+  <si>
+    <t>29.8%</t>
   </si>
   <si>
     <t>3.6%</t>
   </si>
   <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>26.9</t>
-  </si>
-  <si>
-    <t>72.9%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>27.1</t>
+  </si>
+  <si>
+    <t>72.6%</t>
+  </si>
+  <si>
+    <t>10.4%</t>
   </si>
   <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>7.2</t>
+    <t>7.3</t>
   </si>
   <si>
     <t>12.3</t>
   </si>
   <si>
-    <t>18.9</t>
-  </si>
-  <si>
-    <t>72.2%</t>
-  </si>
-  <si>
-    <t>-R$ 18.122,85</t>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>71.8%</t>
+  </si>
+  <si>
+    <t>-R$ 18.373,70</t>
   </si>
   <si>
     <t>2.94</t>
@@ -4874,7 +4874,7 @@
         <v>-236.30000000000001</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -8823,7 +8823,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8859,27 +8859,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>5794.1700000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>5794.1700000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.035534927278771278</v>
+      </c>
+      <c r="R58" s="7">
+        <v>71</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.12698412698412698</v>
+      </c>
+      <c r="T58" s="6">
+        <v>-4.9545442919348242</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-5.3108127479863381</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.014951149172357731</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0010079959683613011</v>
+      </c>
+      <c r="X58" s="8">
+        <v>34.57756346153846</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.28846153846153844</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>4.0748723076923072</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>13.158332692307692</v>
+      </c>
       <c r="AC58" s="8">
         <v>17.158974000000001</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>24.092628846153847</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.48076923076923078</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-250.84999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -11143,7 +11177,7 @@
         <v>-151.69999999999999</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -12706,7 +12740,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12740,25 +12774,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>5082.4700000000003</v>
+      </c>
+      <c r="P89" s="5">
+        <v>5082.4700000000003</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.21098403640128971</v>
+      </c>
+      <c r="R89" s="7">
+        <v>46</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.36986301369863017</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-0.00071130769094554416</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.31492467245256733</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.084290610667647814</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.062830572536581614</v>
+      </c>
+      <c r="X89" s="8">
+        <v>47.762819230769232</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.57692307692307687</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>5.2607645833333327</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>15.513689285714287</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>29.250596428571431</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.23076923076923078</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14288,7 +14356,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -16619,7 +16687,7 @@
         <v>-196</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -24876,7 +24944,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25847,7 +25915,7 @@
         <v>-74.799999999999997</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27158,7 +27226,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28567,7 +28635,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-01).xlsx
@@ -915,48 +915,48 @@
   </si>
   <si>
     <t>215
-179</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>R$ 879.913,10</t>
-  </si>
-  <si>
-    <t>R$ 4.631,12
-R$ 4.731,15</t>
-  </si>
-  <si>
-    <t>2.2%
-5.2%</t>
-  </si>
-  <si>
-    <t>50.7</t>
+182</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>R$ 887.497,85</t>
+  </si>
+  <si>
+    <t>R$ 4.598,43
+R$ 4.694,84</t>
+  </si>
+  <si>
+    <t>2.0%
+4.9%</t>
+  </si>
+  <si>
+    <t>50.4</t>
   </si>
   <si>
     <t>(4.1%)</t>
   </si>
   <si>
-    <t>78.3%</t>
-  </si>
-  <si>
-    <t>29.8%</t>
-  </si>
-  <si>
-    <t>3.6%</t>
+    <t>77.9%</t>
+  </si>
+  <si>
+    <t>29.6%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>27.1</t>
-  </si>
-  <si>
-    <t>72.6%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>72.5%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
   </si>
   <si>
     <t>4.9</t>
@@ -965,16 +965,16 @@
     <t>7.3</t>
   </si>
   <si>
-    <t>12.3</t>
-  </si>
-  <si>
-    <t>19.0</t>
-  </si>
-  <si>
-    <t>71.8%</t>
-  </si>
-  <si>
-    <t>-R$ 18.373,70</t>
+    <t>12.2</t>
+  </si>
+  <si>
+    <t>18.9</t>
+  </si>
+  <si>
+    <t>72.1%</t>
+  </si>
+  <si>
+    <t>-R$ 18.349,70</t>
   </si>
   <si>
     <t>2.94</t>
@@ -20610,7 +20610,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20646,25 +20646,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>3124.9000000000001</v>
+      </c>
+      <c r="P151" s="5">
+        <v>3124.9000000000001</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.068892259192934735</v>
+      </c>
+      <c r="R151" s="7">
+        <v>43</v>
+      </c>
+      <c r="S151" s="6">
+        <v>0.10256410256410264</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.32899804793753401</v>
+      </c>
+      <c r="U151" s="6">
+        <v>0.016648852763288424</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.042840890908509073</v>
+      </c>
+      <c r="W151" s="6">
+        <v>-0.0013493231783417068</v>
+      </c>
+      <c r="X151" s="8">
+        <v>20.2775</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>3.0522727272727277</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.8070824999999999</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>5.7940740000000002</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>12.690417499999999</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.97499999999999998</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21360,7 +21396,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21396,25 +21432,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>2308.9099999999999</v>
+      </c>
+      <c r="P157" s="5">
+        <v>2308.9099999999999</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.19998683339743395</v>
+      </c>
+      <c r="R157" s="7">
+        <v>28</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.22222222222222221</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.34777375471542848</v>
+      </c>
+      <c r="U157" s="6">
+        <v>0.01938070344881351</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.064949478325270371</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.024740028844779573</v>
+      </c>
+      <c r="X157" s="8">
+        <v>22.354545454545455</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>6.3214285714285712</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.9657388888888891</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>10.110436</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>15.785604545454545</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.95454545454545459</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -22366,7 +22438,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22402,25 +22474,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>2150.9400000000001</v>
+      </c>
+      <c r="P165" s="5">
+        <v>2150.9400000000001</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.20408956184851734</v>
+      </c>
+      <c r="R165" s="7">
+        <v>27</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.28947368421052633</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.32696444345262998</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.0081866997684733184</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.042653212084019079</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.018836183250113905</v>
+      </c>
+      <c r="X165" s="8">
+        <v>22.074999999999999</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>3.4294884615384618</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>3.6452357142857141</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>7.699999</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>14.611907142857143</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.9285714285714286</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>24</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
